--- a/2026Ene-PLF.xlsx
+++ b/2026Ene-PLF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lbeltran\Documents\PLF\2026PLF12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD33B9A-04DF-4314-BE32-28CFCF57178E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BD5637-7334-4866-8664-7E316AC586AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="53">
   <si>
     <t>Clave</t>
   </si>
@@ -6792,6 +6792,9 @@
       <c r="H48" s="14">
         <v>2</v>
       </c>
+      <c r="I48" s="14">
+        <v>0</v>
+      </c>
       <c r="J48" s="14">
         <v>2</v>
       </c>
@@ -6801,11 +6804,11 @@
       <c r="L48" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="M48" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="N48" s="14" t="s">
-        <v>52</v>
+      <c r="M48" s="14">
+        <v>1</v>
+      </c>
+      <c r="N48" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="6:14" x14ac:dyDescent="0.25">
@@ -6827,14 +6830,14 @@
       <c r="K49" s="14">
         <v>2</v>
       </c>
-      <c r="L49" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="M49" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="N49" s="14" t="s">
-        <v>52</v>
+      <c r="L49" s="14">
+        <v>1</v>
+      </c>
+      <c r="M49" s="14">
+        <v>1</v>
+      </c>
+      <c r="N49" s="14">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/2026Ene-PLF.xlsx
+++ b/2026Ene-PLF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lbeltran\Documents\PLF\2026PLF12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BD5637-7334-4866-8664-7E316AC586AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DCCD602-4B2F-4D3C-91F6-64FDC2EF0F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="52">
   <si>
     <t>Clave</t>
   </si>
@@ -195,9 +195,6 @@
   </si>
   <si>
     <t>f.and</t>
-  </si>
-  <si>
-    <t>p</t>
   </si>
 </sst>
 </file>
@@ -6743,14 +6740,14 @@
       <c r="K46" s="14">
         <v>2</v>
       </c>
-      <c r="L46" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="M46" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="N46" s="14" t="s">
-        <v>52</v>
+      <c r="L46" s="14">
+        <v>1</v>
+      </c>
+      <c r="M46" s="14">
+        <v>1</v>
+      </c>
+      <c r="N46" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
@@ -6801,8 +6798,8 @@
       <c r="K48" s="14">
         <v>2</v>
       </c>
-      <c r="L48" s="14" t="s">
-        <v>52</v>
+      <c r="L48" s="14">
+        <v>1</v>
       </c>
       <c r="M48" s="14">
         <v>1</v>

--- a/2026Ene-PLF.xlsx
+++ b/2026Ene-PLF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lbeltran\Documents\PLF\2026PLF12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DCCD602-4B2F-4D3C-91F6-64FDC2EF0F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18353B4-6E50-4A4C-AACA-A691DC8C9057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="53">
   <si>
     <t>Clave</t>
   </si>
@@ -196,12 +196,15 @@
   <si>
     <t>f.and</t>
   </si>
+  <si>
+    <t>fnc</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -368,6 +371,14 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="45">
@@ -863,7 +874,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -993,6 +1004,9 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -5853,7 +5867,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{418B29D2-A8FB-4BF3-A97E-3DAB5541EE88}">
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.42578125" style="14" bestFit="1" customWidth="1"/>
@@ -5864,7 +5878,11 @@
     <col min="6" max="6" width="16.5703125" customWidth="1"/>
     <col min="7" max="7" width="7.140625" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.28515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="15" width="11.42578125" style="14"/>
+    <col min="9" max="11" width="11.42578125" style="14"/>
+    <col min="12" max="12" width="7.28515625" style="14" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.5703125" style="14" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.7109375" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6432,7 +6450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="26">
         <v>7</v>
       </c>
@@ -6453,7 +6471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="26">
         <v>7</v>
       </c>
@@ -6474,7 +6492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="28">
         <v>8</v>
       </c>
@@ -6495,7 +6513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="28">
         <v>8</v>
       </c>
@@ -6516,7 +6534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="28">
         <v>8</v>
       </c>
@@ -6537,7 +6555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="28">
         <v>8</v>
       </c>
@@ -6558,7 +6576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="28">
         <v>8</v>
       </c>
@@ -6579,7 +6597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G41" s="14" t="s">
         <v>44</v>
       </c>
@@ -6604,8 +6622,11 @@
       <c r="N41" s="14" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O41" s="14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F42">
         <v>1</v>
       </c>
@@ -6633,8 +6654,11 @@
       <c r="N42" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O42" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F43">
         <v>2</v>
       </c>
@@ -6662,8 +6686,11 @@
       <c r="N43" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O43" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F44">
         <v>3</v>
       </c>
@@ -6691,8 +6718,11 @@
       <c r="N44" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O44" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F45">
         <v>4</v>
       </c>
@@ -6720,8 +6750,11 @@
       <c r="N45" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O45" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F46">
         <v>5</v>
       </c>
@@ -6750,7 +6783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F47">
         <v>6</v>
       </c>
@@ -6779,7 +6812,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F48">
         <v>7</v>
       </c>
@@ -6808,7 +6841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="6:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F49">
         <v>8</v>
       </c>
@@ -6836,6 +6869,12 @@
       <c r="N49" s="14">
         <v>1</v>
       </c>
+      <c r="O49" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="O50" s="44"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I39">
@@ -6852,6 +6891,7 @@
     <mergeCell ref="B8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/2026Ene-PLF.xlsx
+++ b/2026Ene-PLF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lbeltran\Documents\PLF\2026PLF12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18353B4-6E50-4A4C-AACA-A691DC8C9057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C81C15-1051-428B-B9DB-222660C598C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -963,6 +963,9 @@
     <xf numFmtId="0" fontId="0" fillId="44" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1004,9 +1007,6 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2946,1775 +2946,6 @@
         <a:xfrm>
           <a:off x="228600" y="0"/>
           <a:ext cx="5715000" cy="828675"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2773A20D-7EEF-40E5-BAD0-8098DC883137}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="1847850"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 4" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{776427D4-E08F-4258-846A-BA84C38F2BD6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="2419350"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 6" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE9A9C4E-AD1C-415D-BA4A-27E859E79DB3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="2990850"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 8" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33102A63-2F60-42ED-A377-7B9A18D697D0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="6229350"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 10" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BB07B02-B994-4E31-8527-F96F3E3AE3B3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="3562350"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 12" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{363DBE40-D91A-4A34-BF57-4AB2FBD8E76B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="4705350"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 14" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24B7E6F7-1ED9-45F2-AF0E-F3734F76549C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="2609850"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 16" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5E2900C-369A-4281-BDB9-3F435EC2F78A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="4133850"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 18" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FC74E62-9E14-49B9-A166-D8B4A6376BD3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="5276850"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 20" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8293ECB3-BD5A-44EC-B702-20CC217A5279}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="5467350"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 22" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7F2AA62-34B1-4B4C-A225-75E4B2F81379}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="3181350"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Picture 24" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{142DECDF-E8EC-4DD9-BE2C-9CF76848C66F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="5848350"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Picture 26" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2CD53C3-A768-43DB-BA80-21EBB658C4A3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="3752850"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Picture 28" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0ACD5587-9FEE-4B3C-8839-24EA412E47BD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="2038350"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Picture 30" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8E52D89-58F4-4DE3-8103-077BC385C517}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="2228850"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Picture 32" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7381E26C-47D3-499F-BEB5-A5DDE77670D0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="6419850"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="Picture 34" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{614F3F78-2570-4026-B69A-4A1D18F6AF3F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="3371850"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="Picture 36" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A315BE7-4F78-47B4-965D-C2E12CA5BE25}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="4324350"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="Picture 38" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59F5FC74-7F1E-4030-AB50-463E6B434C88}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="4895850"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="Picture 40" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B9C4EA3-D200-4257-83D8-04279A834914}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="5086350"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="Picture 42" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDE65D1B-75D8-4767-B663-01DB8B0432FE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="4514850"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="Picture 44" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14E7D720-56E8-4611-9535-ED9ACE4232E0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="6038850"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="Picture 46" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87950B47-5AC5-432B-82A7-AD7034289BE7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="2800350"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="Picture 48" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{816D1B8B-3863-430E-90F6-0EE93B85719D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="3943350"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="Picture 50" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2402A61A-D482-4F87-97DB-F9E47A98C3FF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="5657850"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="Picture 52" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F598359C-97BB-4E98-97E3-CFC04F9BC2EB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="6610350"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="29" name="Picture 54" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79A4F19A-D92F-4088-B496-701DA5B341F1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="6800850"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="30" name="Picture 56" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16D9B5A0-2DDA-490E-8170-12E1D663D1BA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="6991350"/>
-          <a:ext cx="142875" cy="142875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="Picture 58" descr="itesca">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E748B91D-77B5-4654-A9D9-A4108DE9296E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1104900" y="7181850"/>
-          <a:ext cx="142875" cy="142875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5046,83 +3277,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="39"/>
+      <c r="C6" s="40"/>
       <c r="D6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="39" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="40"/>
+      <c r="E6" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="41"/>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="43"/>
       <c r="D7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="43"/>
+      <c r="F7" s="44"/>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="33"/>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="36"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
@@ -5886,83 +4117,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="39"/>
+      <c r="C6" s="40"/>
       <c r="D6" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="39" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="40"/>
+      <c r="E6" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="41"/>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="43"/>
       <c r="D7" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="43"/>
+      <c r="F7" s="44"/>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="33"/>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="36"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
@@ -6368,7 +4599,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="25">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B29" s="10">
         <v>19</v>
@@ -6473,7 +4704,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="26">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B34" s="10">
         <v>25</v>
@@ -6782,6 +5013,9 @@
       <c r="N46" s="14">
         <v>1</v>
       </c>
+      <c r="O46" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F47">
@@ -6811,6 +5045,9 @@
       <c r="N47" s="14">
         <v>2</v>
       </c>
+      <c r="O47" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F48">
@@ -6874,7 +5111,7 @@
       </c>
     </row>
     <row r="50" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="O50" s="44"/>
+      <c r="O50" s="30"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:I39">
